--- a/Documentation/User Stories.xlsx
+++ b/Documentation/User Stories.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bangs\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bangs\Desktop\GitHub\book-store-management-system-ba\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB59B5E1-504D-41F6-873D-92B212C8C5AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55E0DF3-335B-4A02-B35D-0DA0CADDAFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2820CFB0-9F1D-4BFD-868B-1773CEE5D8F2}"/>
+    <workbookView xWindow="8724" yWindow="0" windowWidth="14412" windowHeight="12336" xr2:uid="{2820CFB0-9F1D-4BFD-868B-1773CEE5D8F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="162">
   <si>
     <t xml:space="preserve">Project Name </t>
   </si>
@@ -620,6 +620,12 @@
 3. Hệ thống tự động tính toán và cập nhật tổng giá trị thanh toán sau khi áp dụng giảm giá.
 4. Khi voucher không hợp lệ hoặc không đáp ứng điều kiện áp dụng, hệ thống hiển thị thông báo phù hợp và không áp dụng giảm giá.
 5. Sau khi áp dụng thành công, hệ thống hiển thị giá trị giảm và tổng tiền thanh toán mới.</t>
+  </si>
+  <si>
+    <t>22/12/2025</t>
+  </si>
+  <si>
+    <t>25/12/2025</t>
   </si>
 </sst>
 </file>
@@ -1097,14 +1103,14 @@
       <c r="A3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="5">
-        <v>46298</v>
+      <c r="B3" s="5" t="s">
+        <v>160</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="5">
-        <v>46359</v>
+      <c r="D3" s="5" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
